--- a/payment_forms/037_hospital_admission_billing_form--payment_forms.xlsx
+++ b/payment_forms/037_hospital_admission_billing_form--payment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -987,8 +987,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'patient_name'}</t>
+          <t>patient_name</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'patient_name'}</t>
+          <t>patient name</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'patient_dob'}</t>
+          <t>patient_dob</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'patient_dob'}</t>
+          <t>patient dob</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'billing_address'}</t>
+          <t>billing_address</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'billing_address'}</t>
+          <t>billing address</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'billing_city'}</t>
+          <t>billing_city</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'billing_city'}</t>
+          <t>billing city</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'billing_state'}</t>
+          <t>billing_state</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'billing_state'}</t>
+          <t>billing state</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'billing_country'}</t>
+          <t>billing_country</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'billing_country'}</t>
+          <t>billing country</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'billing_zip'}</t>
+          <t>billing_zip</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'billing_zip'}</t>
+          <t>billing zip</t>
         </is>
       </c>
     </row>
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'aetna'}</t>
+          <t>aetna</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Aetna'}</t>
+          <t>Aetna</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'blue_cross'}</t>
+          <t>blue_cross</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Blue Cross'}</t>
+          <t>Blue Cross</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'unitedhealth'}</t>
+          <t>unitedhealth</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'UnitedHealth'}</t>
+          <t>UnitedHealth</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Bank Transfer'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'payment_due_next_10_days'}</t>
+          <t>payment_due_next_10_days</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Payment Due Next 10 Days'}</t>
+          <t>Payment Due Next 10 Days</t>
         </is>
       </c>
     </row>
